--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26253-2026 artfynd.xlsx
+++ b/artfynd/A 26253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136922151</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
